--- a/ref/Shortage Emergency Response List_v2.xlsx
+++ b/ref/Shortage Emergency Response List_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wlnyy\Documents\ClaudeCode_Project\02_work_chip_availability\ref\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57ED045A-A282-4E42-A2FA-4C259F1DFFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18C9EC0-36CF-4C76-AE34-34481C745F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{91EA177D-7937-4D81-BE36-BFC059D19307}"/>
+    <workbookView xWindow="5410" yWindow="2310" windowWidth="19200" windowHeight="10060" xr2:uid="{91EA177D-7937-4D81-BE36-BFC059D19307}"/>
   </bookViews>
   <sheets>
     <sheet name="Part List Modify" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="423">
   <si>
     <t>Manufacture</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1658,6 +1658,10 @@
   </si>
   <si>
     <t>ON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prescribed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3946,7 +3950,7 @@
         <v>224</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>414</v>
